--- a/src/sastadev/data/top3000/Woordenlijsten Current.xlsx
+++ b/src/sastadev/data/top3000/Woordenlijsten Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\jodijk\myprograms\python\sastacode\mysastadev\src\sastadev\data\top3000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6079F5-4B95-4769-9FB7-5299BAB0F2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B8A2ED-B369-46EB-8D65-DED5E36900E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70CE039A-4A00-4A81-88A5-4FE1102D9526}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18249" uniqueCount="4046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18256" uniqueCount="4047">
   <si>
     <t>aai</t>
   </si>
@@ -12267,6 +12267,9 @@
   </si>
   <si>
     <t>nonanimate</t>
+  </si>
+  <si>
+    <t>persoon</t>
   </si>
 </sst>
 </file>
@@ -12395,9 +12398,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -12435,7 +12438,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -12541,7 +12544,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12683,7 +12686,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -12692,7 +12695,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DED8EF28-0107-4559-B6C2-41479884DE88}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:M3102"/>
+  <dimension ref="A1:M3103"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="24.6640625" style="7" bestFit="1" customWidth="1"/>
@@ -14574,7 +14577,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1">
+    <row r="66" spans="1:13">
       <c r="A66" s="1" t="s">
         <v>3957</v>
       </c>
@@ -14720,7 +14723,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="71" spans="1:13" hidden="1">
+    <row r="71" spans="1:13">
       <c r="A71" s="1" t="s">
         <v>3946</v>
       </c>
@@ -16052,7 +16055,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="120" spans="1:13" hidden="1">
+    <row r="120" spans="1:13">
       <c r="A120" s="1" t="s">
         <v>3866</v>
       </c>
@@ -16108,7 +16111,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="122" spans="1:13" hidden="1">
+    <row r="122" spans="1:13">
       <c r="A122" s="1" t="s">
         <v>3941</v>
       </c>
@@ -16625,7 +16628,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="141" spans="1:13" hidden="1">
+    <row r="141" spans="1:13">
       <c r="A141" s="1" t="s">
         <v>3942</v>
       </c>
@@ -16654,7 +16657,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="142" spans="1:13" hidden="1">
+    <row r="142" spans="1:13">
       <c r="A142" s="1" t="s">
         <v>3974</v>
       </c>
@@ -17079,7 +17082,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="158" spans="1:13" hidden="1">
+    <row r="158" spans="1:13">
       <c r="A158" s="1" t="s">
         <v>3849</v>
       </c>
@@ -17385,7 +17388,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="169" spans="1:13" hidden="1">
+    <row r="169" spans="1:13">
       <c r="A169" s="1" t="s">
         <v>3933</v>
       </c>
@@ -21083,7 +21086,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="300" spans="1:13" hidden="1">
+    <row r="300" spans="1:13">
       <c r="A300" s="1" t="s">
         <v>3926</v>
       </c>
@@ -21656,7 +21659,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="320" spans="1:13" hidden="1">
+    <row r="320" spans="1:13">
       <c r="A320" s="1" t="s">
         <v>3852</v>
       </c>
@@ -22124,7 +22127,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="336" spans="1:13" hidden="1">
+    <row r="336" spans="1:13">
       <c r="A336" s="1" t="s">
         <v>3853</v>
       </c>
@@ -22441,7 +22444,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="347" spans="1:13" hidden="1">
+    <row r="347" spans="1:13">
       <c r="A347" s="1" t="s">
         <v>3855</v>
       </c>
@@ -23146,7 +23149,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="372" spans="1:13" hidden="1">
+    <row r="372" spans="1:13">
       <c r="A372" s="1" t="s">
         <v>3854</v>
       </c>
@@ -23928,7 +23931,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="400" spans="1:13" hidden="1">
+    <row r="400" spans="1:13">
       <c r="A400" s="1" t="s">
         <v>3867</v>
       </c>
@@ -25986,7 +25989,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="473" spans="1:13" hidden="1">
+    <row r="473" spans="1:13">
       <c r="A473" s="1" t="s">
         <v>3954</v>
       </c>
@@ -27507,7 +27510,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="528" spans="1:13" hidden="1">
+    <row r="528" spans="1:13">
       <c r="A528" s="1" t="s">
         <v>497</v>
       </c>
@@ -30111,7 +30114,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="631" spans="1:13" hidden="1">
+    <row r="631" spans="1:13">
       <c r="A631" s="1" t="s">
         <v>3870</v>
       </c>
@@ -31263,7 +31266,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="676" spans="1:13" hidden="1">
+    <row r="676" spans="1:13">
       <c r="A676" s="1" t="s">
         <v>3967</v>
       </c>
@@ -31468,7 +31471,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="684" spans="1:13" hidden="1">
+    <row r="684" spans="1:13">
       <c r="A684" s="1" t="s">
         <v>3948</v>
       </c>
@@ -31625,7 +31628,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="690" spans="1:13" hidden="1">
+    <row r="690" spans="1:13">
       <c r="A690" s="1" t="s">
         <v>3872</v>
       </c>
@@ -33851,7 +33854,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="776" spans="1:13" hidden="1">
+    <row r="776" spans="1:13">
       <c r="A776" s="1" t="s">
         <v>3945</v>
       </c>
@@ -35063,7 +35066,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="823" spans="1:13" hidden="1">
+    <row r="823" spans="1:13">
       <c r="A823" s="1" t="s">
         <v>3947</v>
       </c>
@@ -35500,7 +35503,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="840" spans="1:13" hidden="1">
+    <row r="840" spans="1:13">
       <c r="A840" s="1" t="s">
         <v>3922</v>
       </c>
@@ -35686,7 +35689,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="847" spans="1:13" hidden="1">
+    <row r="847" spans="1:13">
       <c r="A847" s="1" t="s">
         <v>3959</v>
       </c>
@@ -37401,7 +37404,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="914" spans="1:13" hidden="1">
+    <row r="914" spans="1:13">
       <c r="A914" s="1" t="s">
         <v>3863</v>
       </c>
@@ -40079,7 +40082,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1019" spans="1:13" hidden="1">
+    <row r="1019" spans="1:13">
       <c r="A1019" s="1" t="s">
         <v>3924</v>
       </c>
@@ -40623,7 +40626,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1039" spans="1:13" hidden="1">
+    <row r="1039" spans="1:13">
       <c r="A1039" s="1" t="s">
         <v>3937</v>
       </c>
@@ -41364,7 +41367,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1068" spans="1:13">
+    <row r="1068" spans="1:13" hidden="1">
       <c r="A1068" s="1" t="s">
         <v>1021</v>
       </c>
@@ -42748,7 +42751,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1124" spans="1:13" hidden="1">
+    <row r="1124" spans="1:13">
       <c r="A1124" s="1" t="s">
         <v>3969</v>
       </c>
@@ -42940,7 +42943,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1131" spans="1:13" hidden="1">
+    <row r="1131" spans="1:13">
       <c r="A1131" s="1" t="s">
         <v>1082</v>
       </c>
@@ -43358,7 +43361,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1148" spans="1:13" hidden="1">
+    <row r="1148" spans="1:13">
       <c r="A1148" s="1" t="s">
         <v>3925</v>
       </c>
@@ -45462,7 +45465,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1227" spans="1:13" hidden="1">
+    <row r="1227" spans="1:13">
       <c r="A1227" s="1" t="s">
         <v>3944</v>
       </c>
@@ -47705,7 +47708,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1313" spans="1:13" hidden="1">
+    <row r="1313" spans="1:13">
       <c r="A1313" s="1" t="s">
         <v>3859</v>
       </c>
@@ -49239,7 +49242,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1371" spans="1:13" hidden="1">
+    <row r="1371" spans="1:13">
       <c r="A1371" s="1" t="s">
         <v>3953</v>
       </c>
@@ -50462,7 +50465,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1419" spans="1:13" hidden="1">
+    <row r="1419" spans="1:13">
       <c r="A1419" s="1" t="s">
         <v>3923</v>
       </c>
@@ -52917,7 +52920,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1511" spans="1:13" hidden="1">
+    <row r="1511" spans="1:13">
       <c r="A1511" s="1" t="s">
         <v>3868</v>
       </c>
@@ -53446,7 +53449,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1532" spans="1:13" hidden="1">
+    <row r="1532" spans="1:13">
       <c r="A1532" s="1" t="s">
         <v>3929</v>
       </c>
@@ -54823,7 +54826,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1584" spans="1:13" hidden="1">
+    <row r="1584" spans="1:13">
       <c r="A1584" s="1" t="s">
         <v>3975</v>
       </c>
@@ -56122,7 +56125,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1635" spans="1:13" hidden="1">
+    <row r="1635" spans="1:13">
       <c r="A1635" s="1" t="s">
         <v>3928</v>
       </c>
@@ -60383,7 +60386,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1799" spans="1:13" hidden="1">
+    <row r="1799" spans="1:13">
       <c r="A1799" s="1" t="s">
         <v>3857</v>
       </c>
@@ -60405,7 +60408,7 @@
         <v>3006</v>
       </c>
       <c r="L1799" t="s">
-        <v>3470</v>
+        <v>3006</v>
       </c>
       <c r="M1799" t="s">
         <v>2989</v>
@@ -62787,7 +62790,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1892" spans="1:13" hidden="1">
+    <row r="1892" spans="1:13">
       <c r="A1892" s="1" t="s">
         <v>1821</v>
       </c>
@@ -64353,7 +64356,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="1952" spans="1:13" hidden="1">
+    <row r="1952" spans="1:13">
       <c r="A1952" s="1" t="s">
         <v>3935</v>
       </c>
@@ -68392,7 +68395,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2109" spans="1:13" hidden="1">
+    <row r="2109" spans="1:13">
       <c r="A2109" s="1" t="s">
         <v>3864</v>
       </c>
@@ -68424,7 +68427,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2110" spans="1:13" hidden="1">
+    <row r="2110" spans="1:13">
       <c r="A2110" s="1" t="s">
         <v>3951</v>
       </c>
@@ -69177,7 +69180,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2138" spans="1:13" hidden="1">
+    <row r="2138" spans="1:13">
       <c r="A2138" s="1" t="s">
         <v>3949</v>
       </c>
@@ -69527,7 +69530,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2152" spans="1:13" hidden="1">
+    <row r="2152" spans="1:13">
       <c r="A2152" s="1" t="s">
         <v>3931</v>
       </c>
@@ -69752,7 +69755,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2161" spans="1:13" hidden="1">
+    <row r="2161" spans="1:13">
       <c r="A2161" s="1" t="s">
         <v>3963</v>
       </c>
@@ -70134,7 +70137,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2175" spans="1:13" hidden="1">
+    <row r="2175" spans="1:13">
       <c r="A2175" s="1" t="s">
         <v>3930</v>
       </c>
@@ -70841,7 +70844,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2201" spans="1:13" hidden="1">
+    <row r="2201" spans="1:13">
       <c r="A2201" s="1" t="s">
         <v>3927</v>
       </c>
@@ -72122,7 +72125,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2250" spans="1:13" hidden="1">
+    <row r="2250" spans="1:13">
       <c r="A2250" s="1" t="s">
         <v>3955</v>
       </c>
@@ -75210,7 +75213,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2370" spans="1:13">
+    <row r="2370" spans="1:13" hidden="1">
       <c r="A2370" s="1" t="s">
         <v>2284</v>
       </c>
@@ -75232,7 +75235,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2371" spans="1:13">
+    <row r="2371" spans="1:13" hidden="1">
       <c r="A2371" s="1" t="s">
         <v>2285</v>
       </c>
@@ -75257,7 +75260,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2372" spans="1:13">
+    <row r="2372" spans="1:13" hidden="1">
       <c r="A2372" s="1" t="s">
         <v>2286</v>
       </c>
@@ -76353,7 +76356,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2415" spans="1:13" hidden="1">
+    <row r="2415" spans="1:13">
       <c r="A2415" s="1" t="s">
         <v>3860</v>
       </c>
@@ -76585,7 +76588,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2424" spans="1:13" hidden="1">
+    <row r="2424" spans="1:13">
       <c r="A2424" s="1" t="s">
         <v>3934</v>
       </c>
@@ -78722,7 +78725,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2505" spans="1:13" hidden="1">
+    <row r="2505" spans="1:13">
       <c r="A2505" s="1" t="s">
         <v>3874</v>
       </c>
@@ -80327,7 +80330,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2568" spans="1:13" hidden="1">
+    <row r="2568" spans="1:13">
       <c r="A2568" s="1" t="s">
         <v>3919</v>
       </c>
@@ -80499,7 +80502,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2575" spans="1:13" hidden="1">
+    <row r="2575" spans="1:13">
       <c r="A2575" s="1" t="s">
         <v>3966</v>
       </c>
@@ -81692,7 +81695,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2621" spans="1:13" hidden="1">
+    <row r="2621" spans="1:13">
       <c r="A2621" s="1" t="s">
         <v>3960</v>
       </c>
@@ -82698,7 +82701,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2659" spans="1:13" hidden="1">
+    <row r="2659" spans="1:13">
       <c r="A2659" s="1" t="s">
         <v>3950</v>
       </c>
@@ -84578,7 +84581,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2728" spans="1:13" hidden="1">
+    <row r="2728" spans="1:13">
       <c r="A2728" s="1" t="s">
         <v>3952</v>
       </c>
@@ -85068,7 +85071,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2746" spans="1:13" hidden="1">
+    <row r="2746" spans="1:13">
       <c r="A2746" s="1" t="s">
         <v>2646</v>
       </c>
@@ -85096,7 +85099,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2747" spans="1:13" hidden="1">
+    <row r="2747" spans="1:13">
       <c r="A2747" s="1" t="s">
         <v>3940</v>
       </c>
@@ -85175,7 +85178,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2750" spans="1:13" hidden="1">
+    <row r="2750" spans="1:13">
       <c r="A2750" s="1" t="s">
         <v>3938</v>
       </c>
@@ -88239,7 +88242,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="2866" spans="1:13">
+    <row r="2866" spans="1:13" hidden="1">
       <c r="A2866" s="1" t="s">
         <v>2761</v>
       </c>
@@ -91944,7 +91947,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="3005" spans="1:13" hidden="1">
+    <row r="3005" spans="1:13">
       <c r="A3005" s="1" t="s">
         <v>3856</v>
       </c>
@@ -92173,7 +92176,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="3014" spans="1:13" hidden="1">
+    <row r="3014" spans="1:13">
       <c r="A3014" s="1" t="s">
         <v>3956</v>
       </c>
@@ -93584,7 +93587,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="3067" spans="1:13" hidden="1">
+    <row r="3067" spans="1:13">
       <c r="A3067" s="1" t="s">
         <v>3973</v>
       </c>
@@ -94502,7 +94505,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="3101" spans="1:13" hidden="1">
+    <row r="3101" spans="1:13">
       <c r="A3101" s="1" t="s">
         <v>4040</v>
       </c>
@@ -94529,7 +94532,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="3102" spans="1:13" hidden="1">
+    <row r="3102" spans="1:13">
       <c r="A3102" s="1" t="s">
         <v>2935</v>
       </c>
@@ -94537,7 +94540,7 @@
         <v>2935</v>
       </c>
       <c r="C3102" s="1" t="b">
-        <f t="shared" ref="C3102" si="47">AND(FIND(B3102,A3102),B3102&lt;&gt;"")</f>
+        <f t="shared" ref="C3102:C3103" si="47">AND(FIND(B3102,A3102),B3102&lt;&gt;"")</f>
         <v>1</v>
       </c>
       <c r="F3102" s="1" t="s">
@@ -94556,15 +94559,44 @@
         <v>3006</v>
       </c>
     </row>
+    <row r="3103" spans="1:13">
+      <c r="A3103" s="1" t="s">
+        <v>4046</v>
+      </c>
+      <c r="B3103" s="1" t="s">
+        <v>4046</v>
+      </c>
+      <c r="C3103" s="1" t="b">
+        <f t="shared" si="47"/>
+        <v>1</v>
+      </c>
+      <c r="F3103" s="1" t="s">
+        <v>3470</v>
+      </c>
+      <c r="G3103" t="s">
+        <v>3871</v>
+      </c>
+      <c r="K3103" s="1" t="s">
+        <v>3006</v>
+      </c>
+      <c r="L3103" t="s">
+        <v>3006</v>
+      </c>
+      <c r="M3103" t="s">
+        <v>3006</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L3102" xr:uid="{ED6C27D9-E59B-471F-8509-6B95B79B9B99}">
-    <filterColumn colId="1">
+    <filterColumn colId="5">
       <filters>
-        <filter val="kapstok"/>
-        <filter val="stok"/>
-        <filter val="stokbrood"/>
-        <filter val="stoken"/>
-        <filter val="wandelstok"/>
+        <filter val="n"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters>
+        <filter val="n"/>
+        <filter val="no"/>
       </filters>
     </filterColumn>
   </autoFilter>
